--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_686_Senegal.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_686_Senegal.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rfffc57bccb344654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rfbe46ab30b3e4a68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1399805bdbd14a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R92f97fa55e9641f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7b786c9298d949e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6ac553166a524889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rebd398409a054491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R92ab1c046fb04cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R629e96280ed74638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0df2c97f24594fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re84c16205c2848c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R78f40dfe56f34f7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ686CommercialTable" displayName="EEZ686CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ686CommercialTable" displayName="EEZ686CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ686FunctionalTable" displayName="EEZ686FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ686FunctionalTable" displayName="EEZ686FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ686ValidationTable" displayName="EEZ686ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ686ValidationTable" displayName="EEZ686ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -17846,7 +17800,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R207e64f54c81457f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddc9c778f9d14be0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17856,20 +17810,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -17877,660 +17821,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1228.6832007306</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1228.6832007306</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$257,A2,'Species'!$U$2:$U$257))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>158285.05825140802</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>158285.05825140802</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1769.0024292279</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.430008628802343</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2691.588281356428</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1769.0024292279</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2767.542731040593</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$257,A3,'Species'!$U$2:$U$257))</x:f>
-        <x:v>4895789.814202826</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.430008628802343</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2691.588281356428</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4761426.208200869</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>134363.6060019564</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0282191931842888</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.028219193184288876</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3668.9809333845</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.004236573734653</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>100.980280733283</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3668.9809333845</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>142.33536566563333</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$257,A4,'Species'!$U$2:$U$257))</x:f>
-        <x:v>522225.7427735195</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.004236573734653</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>100.980280733283</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>370494.7246582295</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>151731.01811528997</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.409536244423608</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.40953624442360786</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>13301.9886556663</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.546251025285238</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>351.76370368999915</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>13301.9886556663</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>412.91858531280064</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$257,A5,'Species'!$U$2:$U$257))</x:f>
-        <x:v>5492638.337544652</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.546251025285238</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>351.76370368999915</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4679156.79595953</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>813481.5415851213</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1738521654772427</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.17385216547724275</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>151468.78053348788</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.23007011645028</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>169.85178544936866</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>151468.78053348788</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>191.19238626359189</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$257,A6,'Species'!$U$2:$U$257))</x:f>
-        <x:v>28959677.594633844</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.23007011645028</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>169.85178544936866</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>25727242.81345149</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3232434.7811823525</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1256424874060844</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.12564248740608433</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>12922.572165915199</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.00849556457211</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.1975434529125</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>12922.572165915199</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.253715120959102</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$257,A7,'Species'!$U$2:$U$257))</x:f>
-        <x:v>132504.37361932988</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.00849556457211</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.1975434529125</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>131778.49118531783</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>725.8824340120482</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0055083528994975</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.005508352899497477</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>200690.75732130528</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3567711119120243</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>227.38986923076112</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>200690.75732130528</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>281.00593540111896</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$257,A8,'Species'!$U$2:$U$257))</x:f>
-        <x:v>56395293.98743235</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3567711119120243</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>227.38986923076112</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>45635045.063114025</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>10760248.924318328</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2357891596126775</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.23578915961267763</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>120712.1808243444</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.592217291192284</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>391.03649471656377</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>120712.1808243444</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>551.3096795105288</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$257,A9,'Species'!$U$2:$U$257))</x:f>
-        <x:v>66549793.7232863</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.592217291192284</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>391.03649471656377</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>47202868.05914364</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>19346925.66414266</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.4098675877046623</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.40986758770466236</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>554.5543120285</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.880477067876966</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>759.4113222880778</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>554.5543120285</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>765.8093685526558</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$257,A10,'Species'!$U$2:$U$257))</x:f>
-        <x:v>424682.88752269803</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.880477067876966</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>759.4113222880778</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>421134.8233781185</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3548.064144579519</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.008425007735335</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.008425007735334838</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>6037.319880749001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.251333817158132</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1783.7493060227382</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>6037.319880749001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2606.197316337348</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$257,A11,'Species'!$U$2:$U$257))</x:f>
-        <x:v>15734446.871078163</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.251333817158132</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1783.7493060227382</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>10769065.14752331</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4965381.723554853</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4610782510399059</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.46107825103990585</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>29790.543999560097</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.448782054187128</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2810.490063535665</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>29790.543999560097</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2824.320350131158</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$257,A12,'Species'!$U$2:$U$257))</x:f>
-        <x:v>84138039.65943524</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.448782054187128</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2810.490063535665</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>83726027.89808568</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>412011.76134955883</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0049209519631228</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0049209519631227975</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e9c83c878e44317"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b538df844a3418e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18540,20 +18055,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -18561,1416 +18066,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>17502.804120612604</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7094745045509243</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>512.2411980364265</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>17502.804120612604</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>545.1199638990032</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$257,A2,'Species'!$U$2:$U$257))</x:f>
-        <x:v>9541127.950359667</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7094745045509243</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>512.2411980364265</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>8965657.351739502</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>575470.5986201651</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.064186102149946</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.06418610214994591</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>10.207699090500002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.377271771519801</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2383.8107367606403</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>10.207699090500002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2448.2070260233963</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$257,A3,'Species'!$U$2:$U$257))</x:f>
-        <x:v>24990.56063289474</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.377271771519801</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2383.8107367606403</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>24333.22268955573</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>657.337943339011</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.027014010915256</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0270140109152559</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2.9749273922</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2.9749273922</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$257,A4,'Species'!$U$2:$U$257))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>6508.431982691478</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>6508.431982691478</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5827.2446692741005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.240355424187643</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1739.2236174005193</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5827.2446692741005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2120.5381191713204</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$257,A5,'Species'!$U$2:$U$257))</x:f>
-        <x:v>12356894.450933604</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.240355424187643</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1739.2236174005193</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>10134881.553172793</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2222012.8977608103</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2192440914186307</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.21924409141863074</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>17555.1606318663</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.8809608273728817</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>760.257699889853</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>17555.1606318663</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>834.765307037671</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$257,A6,'Species'!$U$2:$U$257))</x:f>
-        <x:v>14654439.054955507</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.8809608273728817</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>760.257699889853</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>13346446.043179572</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1307993.011775935</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0980030944226054</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09800309442260535</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>26012.138246691502</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.422995722999607</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2648.4740558890344</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>26012.138246691502</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2695.900274026939</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$257,A7,'Species'!$U$2:$U$257))</x:f>
-        <x:v>70126130.62728223</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.422995722999607</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2648.4740558890344</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>68892473.28456132</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1233657.342720911</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0179069974396953</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01790699743969522</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>562.4890806886001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.685038570910007</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>484.21537019847466</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>562.4890806886001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>611.5155105036091</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$257,A8,'Species'!$U$2:$U$257))</x:f>
-        <x:v>343970.7973299951</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.685038570910007</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>484.21537019847466</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>272365.8584382302</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>71604.9388917649</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2628998337102673</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.26289983371026726</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2041.5262838431001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6894240599958996</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>489.1297292528998</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2041.5262838431001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>741.7667820834878</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$257,A9,'Species'!$U$2:$U$257))</x:f>
-        <x:v>1514336.3821051575</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6894240599958996</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>489.1297292528998</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>998571.1984788541</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>515765.18362630333</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.516503164132893</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5165031641328931</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4023.0658885701</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.492128984314071</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>3105.481771062469</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4023.0658885701</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>3595.6482270767374</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$257,A10,'Species'!$U$2:$U$257))</x:f>
-        <x:v>14465529.72964998</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.492128984314071</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>3105.481771062469</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>12493557.78073768</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1971971.9489123002</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1578391026415749</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.1578391026415748</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1353.389835578</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.41320561947149</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>258.94386110747047</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1353.389835578</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>264.09466827607906</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$257,A11,'Species'!$U$2:$U$257))</x:f>
-        <x:v>357423.03967518907</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.41320561947149</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>258.94386110747047</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>350451.9896081719</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>6971.050067017146</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0198915979184802</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.019891597918480167</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1089.4303935480002</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.362566070403909</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2304.443530668588</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1089.4303935480002</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2416.8376512334125</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$257,A12,'Species'!$U$2:$U$257))</x:f>
-        <x:v>2632976.393524841</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.362566070403909</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2304.443530668588</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2510530.822525423</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>122445.57099941792</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0487727813977787</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.048772781397778665</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1874.0996306901</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.080203530603036</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.8280037229065</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1874.0996306901</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.9540621192111</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$257,A13,'Species'!$U$2:$U$257))</x:f>
-        <x:v>2254455.763554769</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.080203530603036</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.8280037229065</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>2254219.5175608094</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>236.24599395971745</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0001048016806346</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.00010480168063461216</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>25069.779478984798</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5511164658468526</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>355.7267019058981</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>25069.779478984798</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>417.24604529584866</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$257,A14,'Species'!$U$2:$U$257))</x:f>
-        <x:v>10460266.344045429</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5511164658468526</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>355.7267019058981</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>8917989.971567426</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1542276.3724780027</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.172939908812987</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.17293990881298696</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>186390.92036081542</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.290774867930441</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>195.33266165994712</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>186390.92036081542</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>214.2110660553138</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$257,A15,'Species'!$U$2:$U$257))</x:f>
-        <x:v>39926997.75352137</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.290774867930441</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>195.33266165994712</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>36408234.583325304</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>3518763.170196064</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0966474538100133</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.09664745381001337</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>117349.17152639241</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.384635988108781</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>242.4577039432742</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>117349.17152639241</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>462.5014207718986</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$257,A16,'Species'!$U$2:$U$257))</x:f>
-        <x:v>54274158.55736172</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.384635988108781</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>242.4577039432742</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>28452210.687934555</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>25821947.869427167</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.907555063212618</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.9075550632126179</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>2430.9905324396004</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.581765733703431</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>381.73829875146475</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>2430.9905324396004</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>505.6083248121697</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$257,A17,'Species'!$U$2:$U$257))</x:f>
-        <x:v>1229129.0507410308</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.581765733703431</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>381.73829875146475</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>928002.1901344105</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>301126.8606066203</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.324489385701779</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.32448938570177893</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>12922.598119680499</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0084964111222456</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.197563330531416</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>12922.598119680499</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.253748584207456</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$257,A18,'Species'!$U$2:$U$257))</x:f>
-        <x:v>132505.07217395585</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0084964111222456</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.197563330531416</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>131779.01272044808</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>726.0594535077689</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0055096744050436</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.005509674405043609</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2315.5910978065</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.765207087876557</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>58.23808525773127</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2315.5910978065</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>71.17090027442396</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$257,A19,'Species'!$U$2:$U$257))</x:f>
-        <x:v>164802.7030983303</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.765207087876557</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>58.23808525773127</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>134855.5917760985</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>29947.111322231794</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2220679982773954</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.2220679982773955</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>3687.1387845199997</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.19</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>154.88166189124811</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>3687.1387845199997</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$257,A20,'Species'!$U$2:$U$257))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>571070.1825701342</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.19</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>571070.1825701342</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>10389.456720632399</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.042770874762308</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>110.34962833380912</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>10389.456720632399</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>119.76673681061357</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$257,A21,'Species'!$U$2:$U$257))</x:f>
-        <x:v>1244311.328665241</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.042770874762308</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>110.34962833380912</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1146472.6877119807</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>97838.64095326024</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0853388327536324</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.08533883275363248</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>88980.3409275476</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.3537708048080974</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>225.82436869350377</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>88980.3409275476</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>232.67142700344795</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$257,A22,'Species'!$U$2:$U$257))</x:f>
-        <x:v>20703182.898865804</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.3537708048080974</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>225.82436869350377</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>20093929.31609617</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>609253.5827696323</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.030320280975687</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.030320280975687113</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1.0917325787999999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1.0917325787999999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$257,A23,'Species'!$U$2:$U$257))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>586.2951079488923</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>586.2951079488923</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>13301.9886556663</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.546251025285238</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>351.76370368999915</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>13301.9886556663</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>412.91858531280064</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$257,A24,'Species'!$U$2:$U$257))</x:f>
-        <x:v>5492638.337544652</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.546251025285238</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>351.76370368999915</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>4679156.79595953</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>813481.5415851213</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.1738521654772427</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.17385216547724275</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>1422.0533809513</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.7999996661348963</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>630.9568594301476</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>1422.0533809513</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>630.9569942227814</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$257,A25,'Species'!$U$2:$U$257))</x:f>
-        <x:v>897254.5268693762</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.7999996661348963</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>630.9568594301476</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>897254.3351870554</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0.19168232078664005</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.000000213632092</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>2.136320921165335e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>29.711530538999998</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.969333021380202</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>931.8221321736099</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>29.711530538999998</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>932.0225759646557</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$257,A26,'Species'!$U$2:$U$257))</x:f>
-        <x:v>27691.817228811316</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.969333021380202</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>931.8221321736099</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>27685.861736992305</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>5.955491819011513</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0002151094979663</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.00021510949796639767</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76496248c2aa49cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e5c4f5b465d4a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20145,7 +18731,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -20244,7 +18830,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>263403378.0497803</x:v>
+        <x:v>223582525.0829516</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20258,7 +18844,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>263403378.04978034</x:v>
+        <x:v>222639224.56650266</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20272,7 +18858,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-39820852.966828704</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20286,7 +18872,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-40764153.48327765</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -20297,9 +18883,9 @@
         <x:v>EEZ_686</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -20311,47 +18897,19 @@
         <x:v>EEZ_686</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_686</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_686</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce5706b89354ed8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2364720137f4673"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20398,7 +18956,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
